--- a/data/dataVO2.xlsx
+++ b/data/dataVO2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_R\bookdown-crc-master-draft\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01223C1-4E93-4A7A-861B-AF21DD33D83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="36" windowWidth="22980" windowHeight="9552"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VO2max" sheetId="1" r:id="rId1"/>
@@ -34,8 +40,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="18">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,13 +586,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -624,7 +638,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -658,6 +672,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -692,9 +707,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -867,11 +883,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -879,23 +895,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>73.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>79.900000000000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>76.900000000000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -903,15 +919,15 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -919,23 +935,23 @@
         <v>82.2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
       <c r="B7">
-        <v>78.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
       <c r="B8">
-        <v>77.900000000000006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>81.900000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -943,15 +959,15 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>72.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -959,7 +975,7 @@
         <v>80.2</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -967,7 +983,7 @@
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -975,7 +991,7 @@
         <v>67.900000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -983,7 +999,7 @@
         <v>67.099999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -991,7 +1007,7 @@
         <v>73.8</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -999,7 +1015,7 @@
         <v>74.7</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1007,7 +1023,7 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1015,23 +1031,23 @@
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19">
-        <v>67.099999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
       <c r="B20">
-        <v>67.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>67.599999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1055,7 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1047,7 +1063,7 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1055,7 +1071,7 @@
         <v>63.9</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1063,7 +1079,7 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1071,7 +1087,7 @@
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1079,7 +1095,7 @@
         <v>67.8</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1087,7 +1103,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1095,7 +1111,7 @@
         <v>65.8</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1103,7 +1119,7 @@
         <v>63.4</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1111,7 +1127,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
